--- a/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Triphammer_2025-10-03.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:E44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1498,6 +1498,60 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Lentz</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Oats</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>43.94</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>43.94</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>H&amp;M/JP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Cup - Portion (2oz)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
